--- a/majMapping/ig/StructureDefinition-FRLMMedicationDispense.xlsx
+++ b/majMapping/ig/StructureDefinition-FRLMMedicationDispense.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-07T13:52:25+00:00</t>
+    <t>2026-10-08T12:48:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/majMapping/ig/StructureDefinition-FRLMMedicationDispense.xlsx
+++ b/majMapping/ig/StructureDefinition-FRLMMedicationDispense.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="879" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="941" uniqueCount="175">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-08T12:48:01+00:00</t>
+    <t>2026-10-08T13:13:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -507,14 +507,38 @@
     <t>Date et heure de dispense du médicament. Si non présent, la date de dispensation est celle du header.</t>
   </si>
   <si>
-    <t>FRLMMedicationDispense.substitutionOccurred</t>
-  </si>
-  <si>
-    <t xml:space="preserve">boolean
-</t>
+    <t>FRLMMedicationDispense.substitution</t>
   </si>
   <si>
     <t>Autorisation de substitution</t>
+  </si>
+  <si>
+    <t>FRLMMedicationDispense.substitution.type</t>
+  </si>
+  <si>
+    <t>Type de substitution</t>
+  </si>
+  <si>
+    <t>jdv-hl7-v3-ActSubstanceAdminSubstitutionCode-cisis (2.16.840.1.113883.1.11.16621)</t>
+  </si>
+  <si>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-hl7-v3-ActSubstanceAdminSubstitutionCode-cisis|20260916095455</t>
+  </si>
+  <si>
+    <t>FRLMMedicationDispense.substitution.reason[x]</t>
+  </si>
+  <si>
+    <t>CodeableConcept
+string</t>
+  </si>
+  <si>
+    <t>Motif de non substitution (Marge thérapeutique étroite, Enfant forme galénique, Contre-indication formelle).</t>
+  </si>
+  <si>
+    <t>Valeur issue du jdv-substitution-medicament-dispensateur-cisis (1.2.250.1.213.1.1.5.861)</t>
+  </si>
+  <si>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-substitution-medicament-dispensateur-cisis|20260916095453</t>
   </si>
   <si>
     <t>FRLMMedicationDispense.dosageInstructions</t>
@@ -836,7 +860,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ27"/>
+  <dimension ref="A1:AJ29"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="57.26171875" customWidth="true" bestFit="true"/>
@@ -863,8 +887,8 @@
     <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="62.36328125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="73.9609375" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="71.640625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="88.87109375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
@@ -3299,7 +3323,7 @@
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="G25" t="s" s="2">
         <v>78</v>
@@ -3314,13 +3338,13 @@
         <v>72</v>
       </c>
       <c r="K25" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="L25" t="s" s="2">
         <v>159</v>
       </c>
-      <c r="L25" t="s" s="2">
-        <v>160</v>
-      </c>
       <c r="M25" t="s" s="2">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -3374,7 +3398,7 @@
         <v>158</v>
       </c>
       <c r="AG25" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AH25" t="s" s="2">
         <v>78</v>
@@ -3388,10 +3412,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -3414,13 +3438,13 @@
         <v>72</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>162</v>
+        <v>131</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -3447,13 +3471,13 @@
         <v>72</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>72</v>
+        <v>134</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>72</v>
+        <v>162</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>72</v>
+        <v>163</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>72</v>
@@ -3471,7 +3495,7 @@
         <v>72</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>73</v>
@@ -3547,13 +3571,13 @@
         <v>72</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>72</v>
+        <v>134</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>72</v>
+        <v>167</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>72</v>
+        <v>168</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>72</v>
@@ -3583,6 +3607,206 @@
         <v>72</v>
       </c>
       <c r="AJ27" t="s" s="2">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="B28" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="C28" s="2"/>
+      <c r="D28" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="E28" s="2"/>
+      <c r="F28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="G28" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H28" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="I28" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J28" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="K28" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="L28" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="M28" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="N28" s="2"/>
+      <c r="O28" s="2"/>
+      <c r="P28" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Q28" s="2"/>
+      <c r="R28" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="S28" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="T28" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="U28" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="V28" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="W28" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="X28" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Y28" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Z28" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AA28" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AB28" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AC28" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AD28" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AE28" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AF28" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="AG28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AH28" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI28" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AJ28" t="s" s="2">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="B29" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="C29" s="2"/>
+      <c r="D29" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="E29" s="2"/>
+      <c r="F29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="G29" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H29" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="I29" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J29" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="K29" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="L29" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="M29" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="N29" s="2"/>
+      <c r="O29" s="2"/>
+      <c r="P29" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Q29" s="2"/>
+      <c r="R29" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="S29" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="T29" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="U29" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="V29" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="W29" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="X29" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Y29" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Z29" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AA29" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AB29" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AC29" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AD29" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AE29" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AF29" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="AG29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AH29" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI29" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AJ29" t="s" s="2">
         <v>72</v>
       </c>
     </row>
